--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8827,0.0115,0.0873,0.0146</t>
-  </si>
-  <si>
-    <t>0.0660,0.0057,0.0013,0.9780</t>
-  </si>
-  <si>
-    <t>0.6796,0.0819,0.0129,0.2661</t>
-  </si>
-  <si>
-    <t>0.0813,0.0045,0.0011,0.9739</t>
-  </si>
-  <si>
-    <t>0.9978,0.0013,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0015,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9931,0.0031,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9948,0.0030,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9954,0.0026,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9937,0.0050,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9970,0.0015,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9953,0.0025,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.5508,0.0801,0.4202,0.0301</t>
-  </si>
-  <si>
-    <t>0.2781,0.0321,0.7326,0.0041</t>
-  </si>
-  <si>
-    <t>0.4890,0.0135,0.5858,0.0096</t>
-  </si>
-  <si>
-    <t>0.3237,0.1226,0.5732,0.0153</t>
-  </si>
-  <si>
-    <t>0.3925,0.0376,0.6536,0.0120</t>
-  </si>
-  <si>
-    <t>0.0373,0.9675,0.0031,0.0003</t>
-  </si>
-  <si>
-    <t>0.0145,0.9801,0.0100,0.0000</t>
-  </si>
-  <si>
-    <t>0.5214,0.5348,0.0257,0.0028</t>
-  </si>
-  <si>
-    <t>0.0177,0.9786,0.0021,0.0009</t>
-  </si>
-  <si>
-    <t>0.0119,0.9854,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.4884,0.0202,0.5184,0.0249</t>
-  </si>
-  <si>
-    <t>0.4595,0.0210,0.5285,0.0404</t>
-  </si>
-  <si>
-    <t>0.0099,0.0024,0.9919,0.0005</t>
-  </si>
-  <si>
-    <t>0.4415,0.0130,0.6038,0.0139</t>
-  </si>
-  <si>
-    <t>0.0476,0.0037,0.9540,0.0076</t>
-  </si>
-  <si>
-    <t>0.0091,0.0041,0.9876,0.0017</t>
-  </si>
-  <si>
-    <t>0.0118,0.0016,0.9801,0.0083</t>
-  </si>
-  <si>
-    <t>0.6254,0.3656,0.0706,0.0089</t>
-  </si>
-  <si>
-    <t>0.5126,0.4489,0.1119,0.0164</t>
-  </si>
-  <si>
-    <t>0.0080,0.0523,0.9722,0.0135</t>
-  </si>
-  <si>
-    <t>0.1350,0.5618,0.4525,0.0216</t>
-  </si>
-  <si>
-    <t>0.8513,0.1383,0.0300,0.0074</t>
-  </si>
-  <si>
-    <t>0.8420,0.1376,0.0369,0.0059</t>
-  </si>
-  <si>
-    <t>0.8270,0.2166,0.0184,0.0015</t>
-  </si>
-  <si>
-    <t>0.0601,0.9044,0.1455,0.0010</t>
-  </si>
-  <si>
-    <t>0.0181,0.8860,0.2309,0.0195</t>
-  </si>
-  <si>
-    <t>0.0466,0.3390,0.7983,0.0486</t>
-  </si>
-  <si>
-    <t>0.0134,0.2613,0.9138,0.0038</t>
-  </si>
-  <si>
-    <t>0.3437,0.0133,0.5877,0.0765</t>
-  </si>
-  <si>
-    <t>0.0972,0.1632,0.7947,0.0520</t>
-  </si>
-  <si>
-    <t>0.0075,0.9675,0.0308,0.0041</t>
-  </si>
-  <si>
-    <t>0.0170,0.0430,0.9498,0.0205</t>
-  </si>
-  <si>
-    <t>0.0052,0.9483,0.0307,0.2584</t>
-  </si>
-  <si>
-    <t>0.0046,0.9828,0.0256,0.0050</t>
-  </si>
-  <si>
-    <t>0.0077,0.9368,0.1835,0.0520</t>
-  </si>
-  <si>
-    <t>0.0006,0.9927,0.1091,0.0006</t>
-  </si>
-  <si>
-    <t>0.0102,0.0808,0.9633,0.0100</t>
-  </si>
-  <si>
-    <t>0.0007,0.4172,0.9841,0.0005</t>
-  </si>
-  <si>
-    <t>0.0256,0.0257,0.9548,0.0012</t>
-  </si>
-  <si>
-    <t>0.0384,0.0065,0.9670,0.0018</t>
-  </si>
-  <si>
-    <t>0.0003,0.0029,0.9980,0.0010</t>
-  </si>
-  <si>
-    <t>0.0028,0.0175,0.9929,0.0007</t>
-  </si>
-  <si>
-    <t>0.9189,0.1283,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.9809,0.0131,0.0018,0.0025</t>
-  </si>
-  <si>
-    <t>0.8563,0.0535,0.1284,0.0200</t>
-  </si>
-  <si>
-    <t>0.0043,0.1549,0.9857,0.0020</t>
-  </si>
-  <si>
-    <t>0.9816,0.0115,0.0048,0.0011</t>
-  </si>
-  <si>
-    <t>0.9940,0.0031,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9128,0.0988,0.0165,0.0018</t>
-  </si>
-  <si>
-    <t>0.0006,0.9311,0.8795,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.0315,0.9899,0.0019</t>
-  </si>
-  <si>
-    <t>0.0097,0.0822,0.9641,0.0051</t>
-  </si>
-  <si>
-    <t>0.0009,0.8938,0.9280,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.0018,0.9959,0.0006</t>
-  </si>
-  <si>
-    <t>0.1129,0.8704,0.0383,0.0048</t>
-  </si>
-  <si>
-    <t>0.0010,0.9982,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.5705,0.1859,0.3217,0.0113</t>
-  </si>
-  <si>
-    <t>0.1701,0.4703,0.4965,0.0034</t>
-  </si>
-  <si>
-    <t>0.0692,0.2163,0.8385,0.0049</t>
-  </si>
-  <si>
-    <t>0.0027,0.9479,0.5333,0.0003</t>
-  </si>
-  <si>
-    <t>0.0051,0.7779,0.8368,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.9918,0.1445,0.0003</t>
-  </si>
-  <si>
-    <t>0.0047,0.8198,0.7754,0.0017</t>
-  </si>
-  <si>
-    <t>0.0177,0.0007,0.0768,0.9300</t>
-  </si>
-  <si>
-    <t>0.0012,0.0107,0.0006,0.9988</t>
-  </si>
-  <si>
-    <t>0.0066,0.0208,0.0019,0.9950</t>
-  </si>
-  <si>
-    <t>0.0085,0.0140,0.0007,0.9951</t>
-  </si>
-  <si>
-    <t>0.0214,0.0103,0.0049,0.9874</t>
-  </si>
-  <si>
-    <t>0.0067,0.0017,0.0006,0.9969</t>
-  </si>
-  <si>
-    <t>0.0016,0.9453,0.7049,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.8764,0.9639,0.0001</t>
-  </si>
-  <si>
-    <t>0.0421,0.6555,0.5110,0.0153</t>
-  </si>
-  <si>
-    <t>0.0017,0.8739,0.8633,0.0007</t>
-  </si>
-  <si>
-    <t>0.0009,0.9118,0.8206,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.7082,0.8393,0.0008</t>
-  </si>
-  <si>
-    <t>0.9890,0.0044,0.0010,0.0025</t>
-  </si>
-  <si>
-    <t>0.9786,0.0157,0.0039,0.0013</t>
-  </si>
-  <si>
-    <t>0.9752,0.0239,0.0031,0.0011</t>
-  </si>
-  <si>
-    <t>0.9951,0.0022,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9917,0.0022,0.0002,0.0030</t>
-  </si>
-  <si>
-    <t>0.9940,0.0077,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9859,0.0083,0.0014,0.0017</t>
-  </si>
-  <si>
-    <t>0.9691,0.0315,0.0052,0.0011</t>
-  </si>
-  <si>
-    <t>0.9938,0.0034,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9945,0.0026,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9967,0.0021,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9951,0.0010,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9905,0.0025,0.0009,0.0024</t>
-  </si>
-  <si>
-    <t>0.9948,0.0027,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9949,0.0018,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9955,0.0016,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.0017,0.0011,0.9619,0.0870</t>
-  </si>
-  <si>
-    <t>0.0567,0.0071,0.9560,0.0010</t>
-  </si>
-  <si>
-    <t>0.5922,0.0108,0.4577,0.0170</t>
-  </si>
-  <si>
-    <t>0.0178,0.0042,0.9861,0.0003</t>
-  </si>
-  <si>
-    <t>0.2037,0.8620,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.1499,0.8685,0.0192,0.0007</t>
-  </si>
-  <si>
-    <t>0.0059,0.9915,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.2432,0.8173,0.0109,0.0005</t>
-  </si>
-  <si>
-    <t>0.1279,0.8875,0.0180,0.0022</t>
-  </si>
-  <si>
-    <t>0.0140,0.9838,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.1130,0.8963,0.0051,0.0029</t>
-  </si>
-  <si>
-    <t>0.6392,0.0458,0.3661,0.0196</t>
-  </si>
-  <si>
-    <t>0.2049,0.0781,0.7028,0.0173</t>
-  </si>
-  <si>
-    <t>0.4987,0.1092,0.4320,0.0443</t>
-  </si>
-  <si>
-    <t>0.3748,0.0934,0.5061,0.0050</t>
-  </si>
-  <si>
-    <t>0.2703,0.0689,0.1800,0.6469</t>
-  </si>
-  <si>
-    <t>0.0033,0.9918,0.0152,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.9830,0.0157,0.0205</t>
-  </si>
-  <si>
-    <t>0.0385,0.9089,0.0632,0.0916</t>
-  </si>
-  <si>
-    <t>0.0023,0.9410,0.7194,0.0024</t>
-  </si>
-  <si>
-    <t>0.0328,0.9587,0.0461,0.0003</t>
-  </si>
-  <si>
-    <t>0.5851,0.2407,0.1860,0.0042</t>
-  </si>
-  <si>
-    <t>0.8452,0.2482,0.0052,0.0006</t>
-  </si>
-  <si>
-    <t>0.9475,0.0404,0.0058,0.0044</t>
-  </si>
-  <si>
-    <t>0.9808,0.0067,0.0050,0.0031</t>
-  </si>
-  <si>
-    <t>0.9752,0.0165,0.0071,0.0012</t>
-  </si>
-  <si>
-    <t>0.9864,0.0061,0.0028,0.0014</t>
-  </si>
-  <si>
-    <t>0.9877,0.0034,0.0015,0.0047</t>
-  </si>
-  <si>
-    <t>0.9435,0.0484,0.0122,0.0054</t>
-  </si>
-  <si>
-    <t>0.9778,0.0109,0.0033,0.0054</t>
-  </si>
-  <si>
-    <t>0.9827,0.0089,0.0032,0.0030</t>
-  </si>
-  <si>
-    <t>0.0062,0.7551,0.7826,0.0005</t>
-  </si>
-  <si>
-    <t>0.0060,0.7630,0.8029,0.0005</t>
-  </si>
-  <si>
-    <t>0.0060,0.6198,0.9090,0.0015</t>
-  </si>
-  <si>
-    <t>0.0062,0.1882,0.9383,0.0004</t>
-  </si>
-  <si>
-    <t>0.3004,0.0165,0.7273,0.0288</t>
-  </si>
-  <si>
-    <t>0.6857,0.1083,0.2019,0.0637</t>
-  </si>
-  <si>
-    <t>0.4232,0.0050,0.7545,0.0021</t>
-  </si>
-  <si>
-    <t>0.7117,0.0806,0.2163,0.0122</t>
-  </si>
-  <si>
-    <t>0.0319,0.0073,0.0026,0.9861</t>
-  </si>
-  <si>
-    <t>0.0006,0.0032,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0028,0.0025,0.0011,0.9978</t>
-  </si>
-  <si>
-    <t>0.0138,0.0006,0.0097,0.9852</t>
-  </si>
-  <si>
-    <t>0.0006,0.8868,0.7481,0.0017</t>
-  </si>
-  <si>
-    <t>0.9816,0.0112,0.0045,0.0013</t>
-  </si>
-  <si>
-    <t>0.5288,0.5407,0.0135,0.0028</t>
-  </si>
-  <si>
-    <t>0.9820,0.0084,0.0009,0.0056</t>
-  </si>
-  <si>
-    <t>0.7360,0.3349,0.0193,0.0013</t>
-  </si>
-  <si>
-    <t>0.9148,0.0109,0.0152,0.0442</t>
-  </si>
-  <si>
-    <t>0.7367,0.0723,0.0391,0.2022</t>
-  </si>
-  <si>
-    <t>0.9886,0.0030,0.0015,0.0023</t>
-  </si>
-  <si>
-    <t>0.0038,0.0791,0.9664,0.0336</t>
-  </si>
-  <si>
-    <t>0.8636,0.0107,0.0771,0.0475</t>
-  </si>
-  <si>
-    <t>0.9562,0.0099,0.0322,0.0025</t>
-  </si>
-  <si>
-    <t>0.5714,0.4105,0.0751,0.0211</t>
-  </si>
-  <si>
-    <t>0.7927,0.1726,0.0519,0.0052</t>
-  </si>
-  <si>
-    <t>0.8930,0.0768,0.0422,0.0031</t>
-  </si>
-  <si>
-    <t>0.2317,0.6489,0.1909,0.0379</t>
-  </si>
-  <si>
-    <t>0.6642,0.3446,0.0589,0.0023</t>
-  </si>
-  <si>
-    <t>0.3443,0.6412,0.1272,0.0165</t>
-  </si>
-  <si>
-    <t>0.9874,0.0066,0.0024,0.0016</t>
-  </si>
-  <si>
-    <t>0.9891,0.0070,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9939,0.0051,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9877,0.0045,0.0009,0.0027</t>
-  </si>
-  <si>
-    <t>0.9856,0.0051,0.0030,0.0037</t>
-  </si>
-  <si>
-    <t>0.9820,0.0088,0.0018,0.0045</t>
-  </si>
-  <si>
-    <t>0.9810,0.0139,0.0018,0.0027</t>
-  </si>
-  <si>
-    <t>0.9894,0.0068,0.0010,0.0012</t>
-  </si>
-  <si>
-    <t>0.2714,0.7925,0.0153,0.0019</t>
-  </si>
-  <si>
-    <t>0.2673,0.7971,0.0122,0.0003</t>
-  </si>
-  <si>
-    <t>0.8456,0.2130,0.0075,0.0003</t>
-  </si>
-  <si>
-    <t>0.5982,0.3649,0.1442,0.0218</t>
-  </si>
-  <si>
-    <t>0.9083,0.1475,0.0056,0.0004</t>
-  </si>
-  <si>
-    <t>0.8959,0.0859,0.0394,0.0068</t>
-  </si>
-  <si>
-    <t>0.9739,0.0215,0.0055,0.0005</t>
-  </si>
-  <si>
-    <t>0.8855,0.1751,0.0039,0.0010</t>
-  </si>
-  <si>
-    <t>0.0042,0.1266,0.9829,0.0019</t>
-  </si>
-  <si>
-    <t>0.9384,0.0782,0.0037,0.0045</t>
-  </si>
-  <si>
-    <t>0.0081,0.0098,0.9849,0.0026</t>
-  </si>
-  <si>
-    <t>0.0299,0.3219,0.8537,0.0167</t>
-  </si>
-  <si>
-    <t>0.4706,0.0341,0.5772,0.0134</t>
-  </si>
-  <si>
-    <t>0.0012,0.1319,0.9862,0.0016</t>
-  </si>
-  <si>
-    <t>0.0782,0.0263,0.9153,0.0048</t>
-  </si>
-  <si>
-    <t>0.0049,0.0031,0.9897,0.0021</t>
-  </si>
-  <si>
-    <t>0.0045,0.0032,0.9947,0.0004</t>
-  </si>
-  <si>
-    <t>0.5319,0.0713,0.3644,0.1026</t>
-  </si>
-  <si>
-    <t>0.2957,0.0185,0.7535,0.0061</t>
-  </si>
-  <si>
-    <t>0.6888,0.0110,0.3831,0.0053</t>
-  </si>
-  <si>
-    <t>0.4608,0.2137,0.3702,0.0267</t>
-  </si>
-  <si>
-    <t>0.4382,0.0322,0.6146,0.0031</t>
-  </si>
-  <si>
-    <t>0.2443,0.0756,0.7125,0.0045</t>
-  </si>
-  <si>
-    <t>0.5335,0.0402,0.5015,0.0081</t>
-  </si>
-  <si>
-    <t>0.3817,0.0509,0.5949,0.0044</t>
-  </si>
-  <si>
-    <t>0.7241,0.4535,0.0035,0.0003</t>
-  </si>
-  <si>
-    <t>0.3487,0.7890,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.2092,0.8560,0.0036,0.0006</t>
-  </si>
-  <si>
-    <t>0.8249,0.2202,0.0191,0.0026</t>
-  </si>
-  <si>
-    <t>0.8419,0.1282,0.0723,0.0059</t>
-  </si>
-  <si>
-    <t>0.3556,0.2232,0.4820,0.0432</t>
-  </si>
-  <si>
-    <t>0.8547,0.0125,0.1205,0.0076</t>
-  </si>
-  <si>
-    <t>0.5771,0.0141,0.3769,0.0471</t>
-  </si>
-  <si>
-    <t>0.5205,0.0315,0.5078,0.0172</t>
-  </si>
-  <si>
-    <t>0.6448,0.0066,0.4107,0.0087</t>
-  </si>
-  <si>
-    <t>0.2210,0.0065,0.5753,0.1534</t>
-  </si>
-  <si>
-    <t>0.1411,0.3295,0.6700,0.0431</t>
-  </si>
-  <si>
-    <t>0.0122,0.4492,0.8880,0.0082</t>
-  </si>
-  <si>
-    <t>0.0544,0.1965,0.8542,0.0238</t>
-  </si>
-  <si>
-    <t>0.0074,0.3604,0.8602,0.0008</t>
-  </si>
-  <si>
-    <t>0.9807,0.0069,0.0010,0.0056</t>
-  </si>
-  <si>
-    <t>0.9895,0.0067,0.0009,0.0015</t>
-  </si>
-  <si>
-    <t>0.9832,0.0156,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.9831,0.0165,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.9810,0.0148,0.0024,0.0018</t>
-  </si>
-  <si>
-    <t>0.9883,0.0069,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9918,0.0035,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9946,0.0026,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.1525,0.0355,0.8467,0.0258</t>
-  </si>
-  <si>
-    <t>0.6017,0.2338,0.2392,0.0179</t>
-  </si>
-  <si>
-    <t>0.8240,0.0129,0.0883,0.0673</t>
-  </si>
-  <si>
-    <t>0.0110,0.0195,0.9832,0.0006</t>
-  </si>
-  <si>
-    <t>0.0026,0.0418,0.9811,0.0079</t>
-  </si>
-  <si>
-    <t>0.0215,0.0238,0.9591,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0141,0.9958,0.0017</t>
-  </si>
-  <si>
-    <t>0.0176,0.0559,0.9354,0.0010</t>
-  </si>
-  <si>
-    <t>0.0805,0.1819,0.8162,0.0068</t>
-  </si>
-  <si>
-    <t>0.0064,0.0449,0.9829,0.0007</t>
-  </si>
-  <si>
-    <t>0.1633,0.0745,0.7507,0.0097</t>
-  </si>
-  <si>
-    <t>0.6693,0.0097,0.3822,0.0064</t>
-  </si>
-  <si>
-    <t>0.5721,0.0096,0.4901,0.0137</t>
-  </si>
-  <si>
-    <t>0.6261,0.0430,0.3590,0.0235</t>
-  </si>
-  <si>
-    <t>0.9922,0.0058,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9912,0.0068,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9967,0.0012,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9796,0.0098,0.0067,0.0033</t>
-  </si>
-  <si>
-    <t>0.9961,0.0004,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9841,0.0201,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0056,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9926,0.0036,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.0375,0.0337,0.9276,0.0014</t>
-  </si>
-  <si>
-    <t>0.0035,0.0829,0.9482,0.0294</t>
-  </si>
-  <si>
-    <t>0.0058,0.0432,0.9848,0.0002</t>
-  </si>
-  <si>
-    <t>0.0320,0.6934,0.4757,0.0077</t>
-  </si>
-  <si>
-    <t>0.0011,0.0020,0.9945,0.0042</t>
-  </si>
-  <si>
-    <t>0.3785,0.0369,0.6319,0.0137</t>
-  </si>
-  <si>
-    <t>0.1486,0.0085,0.8798,0.0047</t>
-  </si>
-  <si>
-    <t>0.0402,0.3194,0.7821,0.0096</t>
-  </si>
-  <si>
-    <t>0.8773,0.0053,0.0474,0.0491</t>
-  </si>
-  <si>
-    <t>0.0036,0.2281,0.0054,0.9915</t>
-  </si>
-  <si>
-    <t>0.0060,0.0072,0.0005,0.9972</t>
-  </si>
-  <si>
-    <t>0.0025,0.0006,0.0033,0.9968</t>
-  </si>
-  <si>
-    <t>0.0103,0.0004,0.0001,0.9974</t>
-  </si>
-  <si>
-    <t>0.7835,0.0407,0.0307,0.1532</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.5881,0.0142,0.1211,0.2776</t>
+  </si>
+  <si>
+    <t>0.0749,0.0131,0.0032,0.9694</t>
+  </si>
+  <si>
+    <t>0.6268,0.0427,0.0324,0.3425</t>
+  </si>
+  <si>
+    <t>0.2470,0.0077,0.0039,0.8946</t>
+  </si>
+  <si>
+    <t>0.9936,0.0013,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9959,0.0023,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9912,0.0034,0.0012,0.0017</t>
+  </si>
+  <si>
+    <t>0.9959,0.0024,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9858,0.0133,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9930,0.0042,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0033,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9936,0.0046,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.6951,0.0056,0.3911,0.0051</t>
+  </si>
+  <si>
+    <t>0.4884,0.0340,0.5196,0.0043</t>
+  </si>
+  <si>
+    <t>0.4213,0.0124,0.6490,0.0004</t>
+  </si>
+  <si>
+    <t>0.2077,0.0282,0.7833,0.0086</t>
+  </si>
+  <si>
+    <t>0.3808,0.3016,0.4000,0.0441</t>
+  </si>
+  <si>
+    <t>0.0059,0.9925,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0175,0.9774,0.0041,0.0010</t>
+  </si>
+  <si>
+    <t>0.1643,0.8689,0.0085,0.0006</t>
+  </si>
+  <si>
+    <t>0.1020,0.9160,0.0050,0.0007</t>
+  </si>
+  <si>
+    <t>0.0105,0.9900,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.5709,0.0129,0.4670,0.0153</t>
+  </si>
+  <si>
+    <t>0.5318,0.0205,0.4370,0.0368</t>
+  </si>
+  <si>
+    <t>0.0343,0.0061,0.9686,0.0019</t>
+  </si>
+  <si>
+    <t>0.4538,0.0031,0.6275,0.0132</t>
+  </si>
+  <si>
+    <t>0.1902,0.0037,0.8847,0.0029</t>
+  </si>
+  <si>
+    <t>0.0196,0.0155,0.9637,0.0092</t>
+  </si>
+  <si>
+    <t>0.0022,0.0014,0.9827,0.0235</t>
+  </si>
+  <si>
+    <t>0.6105,0.4508,0.0430,0.0061</t>
+  </si>
+  <si>
+    <t>0.1245,0.3788,0.6669,0.0062</t>
+  </si>
+  <si>
+    <t>0.0028,0.0150,0.9857,0.0109</t>
+  </si>
+  <si>
+    <t>0.0182,0.8125,0.6547,0.0021</t>
+  </si>
+  <si>
+    <t>0.7012,0.1251,0.1702,0.0761</t>
+  </si>
+  <si>
+    <t>0.7618,0.1437,0.0948,0.0073</t>
+  </si>
+  <si>
+    <t>0.8272,0.1596,0.0447,0.0027</t>
+  </si>
+  <si>
+    <t>0.0259,0.9473,0.1737,0.0016</t>
+  </si>
+  <si>
+    <t>0.0270,0.7458,0.3808,0.0468</t>
+  </si>
+  <si>
+    <t>0.0392,0.1805,0.8853,0.0309</t>
+  </si>
+  <si>
+    <t>0.0265,0.5054,0.8439,0.0073</t>
+  </si>
+  <si>
+    <t>0.0217,0.0915,0.8743,0.1091</t>
+  </si>
+  <si>
+    <t>0.0082,0.7628,0.7336,0.0046</t>
+  </si>
+  <si>
+    <t>0.0030,0.9851,0.0408,0.0005</t>
+  </si>
+  <si>
+    <t>0.0919,0.1235,0.8503,0.0260</t>
+  </si>
+  <si>
+    <t>0.0437,0.8375,0.0485,0.5267</t>
+  </si>
+  <si>
+    <t>0.0025,0.9779,0.0200,0.0557</t>
+  </si>
+  <si>
+    <t>0.0127,0.9597,0.1420,0.0032</t>
+  </si>
+  <si>
+    <t>0.0021,0.9915,0.0605,0.0003</t>
+  </si>
+  <si>
+    <t>0.0383,0.2157,0.8902,0.0067</t>
+  </si>
+  <si>
+    <t>0.0009,0.1468,0.9910,0.0007</t>
+  </si>
+  <si>
+    <t>0.0126,0.0156,0.9820,0.0015</t>
+  </si>
+  <si>
+    <t>0.0837,0.0028,0.9552,0.0009</t>
+  </si>
+  <si>
+    <t>0.0109,0.0280,0.9771,0.0036</t>
+  </si>
+  <si>
+    <t>0.0032,0.1062,0.9848,0.0005</t>
+  </si>
+  <si>
+    <t>0.9810,0.0155,0.0014,0.0018</t>
+  </si>
+  <si>
+    <t>0.9938,0.0021,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9878,0.0064,0.0015,0.0023</t>
+  </si>
+  <si>
+    <t>0.0022,0.1026,0.9889,0.0030</t>
+  </si>
+  <si>
+    <t>0.9747,0.0192,0.0041,0.0017</t>
+  </si>
+  <si>
+    <t>0.9864,0.0056,0.0045,0.0012</t>
+  </si>
+  <si>
+    <t>0.9494,0.0752,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.0060,0.7222,0.9045,0.0021</t>
+  </si>
+  <si>
+    <t>0.0038,0.0866,0.9797,0.0045</t>
+  </si>
+  <si>
+    <t>0.0038,0.0075,0.9847,0.0089</t>
+  </si>
+  <si>
+    <t>0.0004,0.3759,0.9889,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0144,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.0252,0.9599,0.0167,0.0003</t>
+  </si>
+  <si>
+    <t>0.0071,0.9914,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.4700,0.0333,0.5537,0.0447</t>
+  </si>
+  <si>
+    <t>0.6954,0.1490,0.1715,0.0337</t>
+  </si>
+  <si>
+    <t>0.0646,0.1456,0.8663,0.0159</t>
+  </si>
+  <si>
+    <t>0.0020,0.9469,0.6606,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.9068,0.8571,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9892,0.0825,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.9886,0.1742,0.0016</t>
+  </si>
+  <si>
+    <t>0.0164,0.0005,0.3098,0.7316</t>
+  </si>
+  <si>
+    <t>0.0133,0.0035,0.0009,0.9945</t>
+  </si>
+  <si>
+    <t>0.0066,0.0007,0.0001,0.9977</t>
+  </si>
+  <si>
+    <t>0.0107,0.0109,0.0069,0.9903</t>
+  </si>
+  <si>
+    <t>0.0848,0.0032,0.0041,0.9612</t>
+  </si>
+  <si>
+    <t>0.0022,0.0116,0.0007,0.9983</t>
+  </si>
+  <si>
+    <t>0.0002,0.9672,0.8769,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.5557,0.9463,0.0012</t>
+  </si>
+  <si>
+    <t>0.0097,0.5360,0.8587,0.0021</t>
+  </si>
+  <si>
+    <t>0.0025,0.8123,0.8287,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.8861,0.7692,0.0001</t>
+  </si>
+  <si>
+    <t>0.0045,0.9143,0.6712,0.0008</t>
+  </si>
+  <si>
+    <t>0.9970,0.0023,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9871,0.0136,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9598,0.0452,0.0050,0.0004</t>
+  </si>
+  <si>
+    <t>0.9944,0.0039,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9868,0.0072,0.0027,0.0020</t>
+  </si>
+  <si>
+    <t>0.9895,0.0068,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.9864,0.0072,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.9897,0.0067,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9947,0.0012,0.0002,0.0018</t>
+  </si>
+  <si>
+    <t>0.9957,0.0021,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9926,0.0025,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9967,0.0006,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9884,0.0105,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9961,0.0006,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9952,0.0028,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9925,0.0029,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9984,0.0026</t>
+  </si>
+  <si>
+    <t>0.1459,0.0959,0.7687,0.0100</t>
+  </si>
+  <si>
+    <t>0.5600,0.0160,0.4655,0.0187</t>
+  </si>
+  <si>
+    <t>0.0491,0.0070,0.9644,0.0011</t>
+  </si>
+  <si>
+    <t>0.0818,0.9149,0.0123,0.0005</t>
+  </si>
+  <si>
+    <t>0.0104,0.9725,0.0472,0.0005</t>
+  </si>
+  <si>
+    <t>0.0466,0.9487,0.0047,0.0009</t>
+  </si>
+  <si>
+    <t>0.2342,0.8356,0.0044,0.0001</t>
+  </si>
+  <si>
+    <t>0.0138,0.9789,0.0083,0.0005</t>
+  </si>
+  <si>
+    <t>0.0296,0.9579,0.0146,0.0002</t>
+  </si>
+  <si>
+    <t>0.7288,0.3688,0.0067,0.0010</t>
+  </si>
+  <si>
+    <t>0.3571,0.4950,0.2793,0.0324</t>
+  </si>
+  <si>
+    <t>0.3509,0.0224,0.6933,0.0129</t>
+  </si>
+  <si>
+    <t>0.4258,0.0461,0.5747,0.0065</t>
+  </si>
+  <si>
+    <t>0.2590,0.0220,0.7833,0.0053</t>
+  </si>
+  <si>
+    <t>0.0514,0.2108,0.0349,0.9475</t>
+  </si>
+  <si>
+    <t>0.0007,0.9970,0.0102,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.9843,0.0241,0.0119</t>
+  </si>
+  <si>
+    <t>0.0255,0.9408,0.0251,0.0383</t>
+  </si>
+  <si>
+    <t>0.0010,0.9737,0.5928,0.0002</t>
+  </si>
+  <si>
+    <t>0.0192,0.9702,0.0425,0.0002</t>
+  </si>
+  <si>
+    <t>0.3068,0.6239,0.1264,0.0068</t>
+  </si>
+  <si>
+    <t>0.8333,0.2412,0.0079,0.0006</t>
+  </si>
+  <si>
+    <t>0.7126,0.3324,0.0338,0.0020</t>
+  </si>
+  <si>
+    <t>0.9874,0.0022,0.0019,0.0053</t>
+  </si>
+  <si>
+    <t>0.9872,0.0060,0.0016,0.0021</t>
+  </si>
+  <si>
+    <t>0.9872,0.0030,0.0026,0.0031</t>
+  </si>
+  <si>
+    <t>0.9851,0.0044,0.0015,0.0059</t>
+  </si>
+  <si>
+    <t>0.8948,0.0785,0.0452,0.0206</t>
+  </si>
+  <si>
+    <t>0.9866,0.0056,0.0010,0.0031</t>
+  </si>
+  <si>
+    <t>0.9887,0.0027,0.0010,0.0042</t>
+  </si>
+  <si>
+    <t>0.0024,0.7968,0.8648,0.0007</t>
+  </si>
+  <si>
+    <t>0.0035,0.1494,0.9828,0.0002</t>
+  </si>
+  <si>
+    <t>0.0085,0.2946,0.9318,0.0030</t>
+  </si>
+  <si>
+    <t>0.0162,0.2320,0.9042,0.0016</t>
+  </si>
+  <si>
+    <t>0.5089,0.2302,0.1325,0.1895</t>
+  </si>
+  <si>
+    <t>0.6583,0.0569,0.3098,0.0331</t>
+  </si>
+  <si>
+    <t>0.6732,0.0128,0.3702,0.0120</t>
+  </si>
+  <si>
+    <t>0.7063,0.0170,0.3114,0.0072</t>
+  </si>
+  <si>
+    <t>0.1335,0.0630,0.0277,0.9084</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0004,0.9994</t>
+  </si>
+  <si>
+    <t>0.0041,0.0015,0.0025,0.9962</t>
+  </si>
+  <si>
+    <t>0.0382,0.0005,0.0013,0.9853</t>
+  </si>
+  <si>
+    <t>0.0017,0.7523,0.8898,0.0006</t>
+  </si>
+  <si>
+    <t>0.9491,0.0648,0.0032,0.0019</t>
+  </si>
+  <si>
+    <t>0.8461,0.1381,0.0308,0.0193</t>
+  </si>
+  <si>
+    <t>0.9710,0.0157,0.0052,0.0053</t>
+  </si>
+  <si>
+    <t>0.8949,0.0915,0.0286,0.0040</t>
+  </si>
+  <si>
+    <t>0.9404,0.0152,0.0535,0.0037</t>
+  </si>
+  <si>
+    <t>0.2094,0.0162,0.0132,0.8985</t>
+  </si>
+  <si>
+    <t>0.9843,0.0061,0.0057,0.0009</t>
+  </si>
+  <si>
+    <t>0.0032,0.0640,0.9649,0.0390</t>
+  </si>
+  <si>
+    <t>0.9606,0.0036,0.0085,0.0162</t>
+  </si>
+  <si>
+    <t>0.9305,0.0113,0.0316,0.0153</t>
+  </si>
+  <si>
+    <t>0.4870,0.5534,0.0405,0.0146</t>
+  </si>
+  <si>
+    <t>0.7347,0.2196,0.0457,0.0076</t>
+  </si>
+  <si>
+    <t>0.8167,0.1069,0.0918,0.0041</t>
+  </si>
+  <si>
+    <t>0.3608,0.5399,0.0868,0.1497</t>
+  </si>
+  <si>
+    <t>0.7778,0.1932,0.0341,0.0055</t>
+  </si>
+  <si>
+    <t>0.7860,0.1889,0.0593,0.0168</t>
+  </si>
+  <si>
+    <t>0.9869,0.0058,0.0045,0.0012</t>
+  </si>
+  <si>
+    <t>0.9869,0.0052,0.0020,0.0032</t>
+  </si>
+  <si>
+    <t>0.9905,0.0065,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9884,0.0015,0.0006,0.0060</t>
+  </si>
+  <si>
+    <t>0.9764,0.0133,0.0049,0.0049</t>
+  </si>
+  <si>
+    <t>0.9878,0.0069,0.0020,0.0015</t>
+  </si>
+  <si>
+    <t>0.9778,0.0044,0.0010,0.0141</t>
+  </si>
+  <si>
+    <t>0.9934,0.0008,0.0002,0.0030</t>
+  </si>
+  <si>
+    <t>0.6789,0.4241,0.0151,0.0040</t>
+  </si>
+  <si>
+    <t>0.2990,0.7868,0.0093,0.0002</t>
+  </si>
+  <si>
+    <t>0.7564,0.2573,0.0242,0.0013</t>
+  </si>
+  <si>
+    <t>0.7599,0.1482,0.0172,0.0516</t>
+  </si>
+  <si>
+    <t>0.9595,0.0449,0.0045,0.0013</t>
+  </si>
+  <si>
+    <t>0.9622,0.0198,0.0023,0.0086</t>
+  </si>
+  <si>
+    <t>0.9723,0.0173,0.0069,0.0013</t>
+  </si>
+  <si>
+    <t>0.7971,0.2583,0.0166,0.0023</t>
+  </si>
+  <si>
+    <t>0.0013,0.0528,0.9954,0.0003</t>
+  </si>
+  <si>
+    <t>0.9062,0.0935,0.0228,0.0022</t>
+  </si>
+  <si>
+    <t>0.0030,0.0022,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.0175,0.9793,0.0251</t>
+  </si>
+  <si>
+    <t>0.0253,0.0072,0.9751,0.0012</t>
+  </si>
+  <si>
+    <t>0.0016,0.6337,0.9599,0.0008</t>
+  </si>
+  <si>
+    <t>0.0036,0.0075,0.9944,0.0004</t>
+  </si>
+  <si>
+    <t>0.0264,0.0023,0.9836,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.1403,0.9905,0.0004</t>
+  </si>
+  <si>
+    <t>0.4994,0.0655,0.4679,0.0136</t>
+  </si>
+  <si>
+    <t>0.1865,0.0209,0.8316,0.0074</t>
+  </si>
+  <si>
+    <t>0.2960,0.0447,0.6959,0.0077</t>
+  </si>
+  <si>
+    <t>0.3717,0.0784,0.5632,0.0061</t>
+  </si>
+  <si>
+    <t>0.4033,0.0354,0.6235,0.0054</t>
+  </si>
+  <si>
+    <t>0.4972,0.0346,0.5155,0.0034</t>
+  </si>
+  <si>
+    <t>0.6267,0.0128,0.4563,0.0067</t>
+  </si>
+  <si>
+    <t>0.4937,0.0722,0.4395,0.0084</t>
+  </si>
+  <si>
+    <t>0.5724,0.5060,0.0144,0.0004</t>
+  </si>
+  <si>
+    <t>0.4032,0.7410,0.0049,0.0003</t>
+  </si>
+  <si>
+    <t>0.6093,0.5626,0.0040,0.0007</t>
+  </si>
+  <si>
+    <t>0.9891,0.0072,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9300,0.0608,0.0212,0.0019</t>
+  </si>
+  <si>
+    <t>0.6587,0.0365,0.3343,0.0042</t>
+  </si>
+  <si>
+    <t>0.6653,0.0339,0.3431,0.0078</t>
+  </si>
+  <si>
+    <t>0.5598,0.0270,0.3822,0.0575</t>
+  </si>
+  <si>
+    <t>0.6245,0.0099,0.4566,0.0085</t>
+  </si>
+  <si>
+    <t>0.7368,0.0419,0.2184,0.0241</t>
+  </si>
+  <si>
+    <t>0.0328,0.0129,0.9432,0.0212</t>
+  </si>
+  <si>
+    <t>0.0601,0.4095,0.6813,0.0434</t>
+  </si>
+  <si>
+    <t>0.0075,0.0754,0.9651,0.0044</t>
+  </si>
+  <si>
+    <t>0.0837,0.0532,0.8757,0.0201</t>
+  </si>
+  <si>
+    <t>0.0183,0.1331,0.9210,0.0097</t>
+  </si>
+  <si>
+    <t>0.9936,0.0028,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9850,0.0081,0.0010,0.0034</t>
+  </si>
+  <si>
+    <t>0.9565,0.0542,0.0036,0.0006</t>
+  </si>
+  <si>
+    <t>0.9898,0.0110,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9925,0.0029,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.9811,0.0188,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9916,0.0044,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9861,0.0100,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.0463,0.0574,0.9193,0.0256</t>
+  </si>
+  <si>
+    <t>0.5557,0.0918,0.4478,0.0115</t>
+  </si>
+  <si>
+    <t>0.9429,0.0311,0.0104,0.0110</t>
+  </si>
+  <si>
+    <t>0.0089,0.0183,0.9842,0.0008</t>
+  </si>
+  <si>
+    <t>0.0070,0.0161,0.9824,0.0045</t>
+  </si>
+  <si>
+    <t>0.0560,0.0402,0.9225,0.0036</t>
+  </si>
+  <si>
+    <t>0.0009,0.0114,0.9931,0.0035</t>
+  </si>
+  <si>
+    <t>0.0942,0.0463,0.8742,0.0068</t>
+  </si>
+  <si>
+    <t>0.0079,0.0290,0.9849,0.0013</t>
+  </si>
+  <si>
+    <t>0.0018,0.0010,0.9950,0.0027</t>
+  </si>
+  <si>
+    <t>0.2419,0.0395,0.7332,0.0093</t>
+  </si>
+  <si>
+    <t>0.4990,0.0551,0.4972,0.0126</t>
+  </si>
+  <si>
+    <t>0.5497,0.0139,0.5223,0.0053</t>
+  </si>
+  <si>
+    <t>0.7018,0.0117,0.2996,0.0186</t>
+  </si>
+  <si>
+    <t>0.9760,0.0218,0.0017,0.0015</t>
+  </si>
+  <si>
+    <t>0.9925,0.0079,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9940,0.0027,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9905,0.0032,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.9846,0.0048,0.0020,0.0037</t>
+  </si>
+  <si>
+    <t>0.9889,0.0096,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0046,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9914,0.0063,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0601,0.0455,0.9201,0.0031</t>
+  </si>
+  <si>
+    <t>0.0170,0.3536,0.8808,0.0076</t>
+  </si>
+  <si>
+    <t>0.0079,0.1142,0.9493,0.0034</t>
+  </si>
+  <si>
+    <t>0.0707,0.0404,0.8822,0.0041</t>
+  </si>
+  <si>
+    <t>0.0068,0.0330,0.9837,0.0014</t>
+  </si>
+  <si>
+    <t>0.1388,0.0058,0.1816,0.6940</t>
+  </si>
+  <si>
+    <t>0.2038,0.0135,0.8176,0.0145</t>
+  </si>
+  <si>
+    <t>0.0365,0.0363,0.9299,0.0193</t>
+  </si>
+  <si>
+    <t>0.6643,0.0406,0.0344,0.2900</t>
+  </si>
+  <si>
+    <t>0.0113,0.0038,0.0106,0.9886</t>
+  </si>
+  <si>
+    <t>0.0319,0.0273,0.0024,0.9830</t>
+  </si>
+  <si>
+    <t>0.0023,0.0003,0.0005,0.9983</t>
+  </si>
+  <si>
+    <t>0.0024,0.0027,0.0002,0.9988</t>
+  </si>
+  <si>
+    <t>0.3762,0.4512,0.0605,0.1828</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2511,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2539,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2861,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +3001,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3606,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3897,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,10 +4233,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4376,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4541,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4656,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4670,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5048,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5381,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
